--- a/artfynd/A 12049-2023 artfynd.xlsx
+++ b/artfynd/A 12049-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120687750</v>
       </c>
       <c r="B2" t="n">
-        <v>57317</v>
+        <v>57447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12049-2023 artfynd.xlsx
+++ b/artfynd/A 12049-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120687750</v>
       </c>
       <c r="B2" t="n">
-        <v>57447</v>
+        <v>57450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12049-2023 artfynd.xlsx
+++ b/artfynd/A 12049-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120687750</v>
       </c>
       <c r="B2" t="n">
-        <v>57450</v>
+        <v>57456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12049-2023 artfynd.xlsx
+++ b/artfynd/A 12049-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120687750</v>
       </c>
       <c r="B2" t="n">
-        <v>57456</v>
+        <v>57459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12049-2023 artfynd.xlsx
+++ b/artfynd/A 12049-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120687750</v>
       </c>
       <c r="B2" t="n">
-        <v>57459</v>
+        <v>57460</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
